--- a/Output/triple_differences_key_coefficients.xlsx
+++ b/Output/triple_differences_key_coefficients.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
-    <t xml:space="preserve">0.013 (0.039)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.195 (0.149)</t>
+    <t xml:space="preserve">0.018 (0.039)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.218 (0.149)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_mean_educ</t>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">-0.098 (0.102)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.046** (0.020)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.080 (0.087)</t>
+    <t xml:space="preserve">-0.040* (0.022)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.109 (0.098)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_mean_izq_der</t>
@@ -74,10 +74,10 @@
     <t xml:space="preserve">0.108 (0.357)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.034 (0.142)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.032 (0.493)</t>
+    <t xml:space="preserve">-0.034 (0.130)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.079 (0.423)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_desempleado</t>
@@ -89,10 +89,10 @@
     <t xml:space="preserve">0.137 (5.436)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.632* (1.349)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.931 (5.812)</t>
+    <t xml:space="preserve">2.519* (1.305)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.753 (5.597)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_en_pareja</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">2.402** (1.025)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.897*** (0.326)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.284* (1.166)</t>
+    <t xml:space="preserve">-0.945*** (0.273)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.495** (1.162)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_hombre</t>
@@ -119,10 +119,10 @@
     <t xml:space="preserve">-7.793 (8.868)</t>
   </si>
   <si>
-    <t xml:space="preserve">4.085 (2.686)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.166 (10.565)</t>
+    <t xml:space="preserve">5.015* (2.681)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-11.121 (10.699)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_interes_pol_mucho</t>
@@ -134,25 +134,10 @@
     <t xml:space="preserve">-2.034 (1.770)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.665 (0.474)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.007* (1.553)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mun_pre_all_share_rural</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.048 (0.070)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893*** (0.311)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.073 (0.066)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.088*** (0.290)</t>
+    <t xml:space="preserve">-0.536 (0.512)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.299* (1.734)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_voto_blanco_nulo</t>
@@ -164,10 +149,25 @@
     <t xml:space="preserve">1.815 (5.587)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.651 (1.300)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.454 (5.506)</t>
+    <t xml:space="preserve">0.624 (1.278)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.821 (5.230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">popdensgeo2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.007 (0.012)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.033 (0.041)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.010 (0.014)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.033 (0.048)</t>
   </si>
 </sst>
 </file>
@@ -799,7 +799,7 @@
         <v>49</v>
       </c>
       <c r="E18" t="n">
-        <v>7467</v>
+        <v>7503</v>
       </c>
     </row>
     <row r="19">
